--- a/cet4/result/11_都市女帝_修仙归来当总裁/11_都市女帝_修仙归来当总裁_学习版.xlsx
+++ b/cet4/result/11_都市女帝_修仙归来当总裁/11_都市女帝_修仙归来当总裁_学习版.xlsx
@@ -397,773 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>lamp</v>
       </c>
       <c r="B2" t="str">
-        <v>lamp</v>
+        <v>/læmp/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>灯</v>
       </c>
-      <c r="D2" t="str">
-        <v>lamp(灯)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>glitter</v>
       </c>
       <c r="B3" t="str">
-        <v>glitter</v>
+        <v>/ˈɡlɪtər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D3" t="str">
         <v>闪耀</v>
       </c>
-      <c r="D3" t="str">
-        <v>glitter(闪耀)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>factory</v>
       </c>
       <c r="B4" t="str">
-        <v>factory</v>
+        <v>/ˈfæktri,ˈfæktəri/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>工厂</v>
       </c>
-      <c r="D4" t="str">
-        <v>factory(工厂)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>skillful</v>
       </c>
       <c r="B5" t="str">
-        <v>skillful</v>
+        <v>/ˈskɪlfl/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>熟练的</v>
       </c>
-      <c r="D5" t="str">
-        <v>skillful(熟练的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>understand</v>
       </c>
       <c r="B6" t="str">
-        <v>understand</v>
+        <v>/ˌʌndərˈstænd/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>明白</v>
       </c>
-      <c r="D6" t="str">
-        <v>understand(明白)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>wheat</v>
       </c>
       <c r="B7" t="str">
-        <v>wheat</v>
+        <v>/wiːt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>小麦</v>
       </c>
-      <c r="D7" t="str">
-        <v>wheat(小麦)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>southern</v>
       </c>
       <c r="B8" t="str">
-        <v>southern</v>
+        <v>/ˈsʌðərn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>南方</v>
       </c>
-      <c r="D8" t="str">
-        <v>southern(南方)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>magic</v>
       </c>
       <c r="B9" t="str">
-        <v>magic</v>
+        <v>/ˈmædʒɪk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>魔法</v>
       </c>
-      <c r="D9" t="str">
-        <v>magic(魔法)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>fly</v>
       </c>
       <c r="B10" t="str">
-        <v>fly</v>
+        <v>/flaɪ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>飞</v>
       </c>
-      <c r="D10" t="str">
-        <v>fly(飞)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>chapter</v>
       </c>
       <c r="B11" t="str">
-        <v>chapter</v>
+        <v>/ˈtʃæptər/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>章节</v>
       </c>
-      <c r="D11" t="str">
-        <v>chapter(章节)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>amaze</v>
       </c>
       <c r="B12" t="str">
-        <v>amaze</v>
+        <v>/əˈmeɪz/</v>
       </c>
       <c r="C12" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>震惊</v>
       </c>
-      <c r="D12" t="str">
-        <v>amaze(震惊)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>compete</v>
       </c>
       <c r="B13" t="str">
-        <v>compete</v>
+        <v>/kəmˈpiːt/</v>
       </c>
       <c r="C13" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>竞争</v>
       </c>
-      <c r="D13" t="str">
-        <v>compete(竞争)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>bad</v>
       </c>
       <c r="B14" t="str">
-        <v>bad</v>
+        <v>/bæd/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>强大的</v>
       </c>
-      <c r="D14" t="str">
-        <v>bad(强大的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>scene</v>
       </c>
       <c r="B15" t="str">
-        <v>scene</v>
+        <v>/siːn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>场景</v>
       </c>
-      <c r="D15" t="str">
-        <v>scene(场景)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>shoe</v>
       </c>
       <c r="B16" t="str">
-        <v>shoe</v>
+        <v>/ʃuː/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>鞋</v>
       </c>
-      <c r="D16" t="str">
-        <v>shoe(鞋)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>cube</v>
       </c>
       <c r="B17" t="str">
-        <v>cube</v>
+        <v>/kjuːb/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>立方体</v>
       </c>
-      <c r="D17" t="str">
-        <v>cube(立方体)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>loud</v>
       </c>
       <c r="B18" t="str">
-        <v>loud</v>
+        <v>/laʊd/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D18" t="str">
         <v>大声的</v>
       </c>
-      <c r="D18" t="str">
-        <v>loud(大声的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>tenth</v>
       </c>
       <c r="B19" t="str">
-        <v>tenth</v>
+        <v>/tenθ/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D19" t="str">
         <v>第十</v>
       </c>
-      <c r="D19" t="str">
-        <v>tenth(第十)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>master</v>
       </c>
       <c r="B20" t="str">
-        <v>master</v>
+        <v>/ˈmæstər/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>主人</v>
       </c>
-      <c r="D20" t="str">
-        <v>master(主人)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>allow</v>
       </c>
       <c r="B21" t="str">
-        <v>allow</v>
+        <v>/əˈlaʊ/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>允许</v>
       </c>
-      <c r="D21" t="str">
-        <v>allow(允许)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>staff</v>
       </c>
       <c r="B22" t="str">
-        <v>staff</v>
+        <v>/stæf/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>职员</v>
       </c>
-      <c r="D22" t="str">
-        <v>staff(职员)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>disposal</v>
       </c>
       <c r="B23" t="str">
-        <v>disposal</v>
+        <v>/dɪˈspoʊzl/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>处理</v>
       </c>
-      <c r="D23" t="str">
-        <v>disposal(处理)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>final</v>
       </c>
       <c r="B24" t="str">
-        <v>final</v>
+        <v>/ˈfaɪnl/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>最终</v>
       </c>
-      <c r="D24" t="str">
-        <v>final(最终)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>interest</v>
       </c>
       <c r="B25" t="str">
-        <v>interest</v>
+        <v>/ˈɪntrəst/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>兴趣</v>
       </c>
-      <c r="D25" t="str">
-        <v>interest(兴趣)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>amount</v>
       </c>
       <c r="B26" t="str">
-        <v>amount</v>
+        <v>/əˈmaʊnt/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D26" t="str">
         <v>数量</v>
       </c>
-      <c r="D26" t="str">
-        <v>amount(数量)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>mobile</v>
       </c>
       <c r="B27" t="str">
-        <v>mobile</v>
+        <v>/ˈmoʊbl/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>灵活的</v>
       </c>
-      <c r="D27" t="str">
-        <v>mobile(灵活的)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>application</v>
       </c>
       <c r="B28" t="str">
-        <v>application</v>
+        <v>/ˌæplɪˈkeɪʃn/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>应用</v>
       </c>
-      <c r="D28" t="str">
-        <v>application(应用)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>appetite</v>
       </c>
       <c r="B29" t="str">
-        <v>appetite</v>
+        <v>/ˈæpɪtaɪt/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>食欲</v>
       </c>
-      <c r="D29" t="str">
-        <v>appetite(食欲)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>establish</v>
       </c>
       <c r="B30" t="str">
-        <v>establish</v>
+        <v>/ɪˈstæblɪʃ/</v>
       </c>
       <c r="C30" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D30" t="str">
         <v>建立</v>
       </c>
-      <c r="D30" t="str">
-        <v>establish(建立)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>snowstorm</v>
       </c>
       <c r="B31" t="str">
-        <v>snowstorm</v>
+        <v>/ˈsnoʊstɔːrm/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>暴风雪</v>
       </c>
-      <c r="D31" t="str">
-        <v>snowstorm(暴风雪)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>overcome</v>
       </c>
       <c r="B32" t="str">
-        <v>overcome</v>
+        <v>/ˌoʊvərˈkʌm/</v>
       </c>
       <c r="C32" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>克服</v>
       </c>
-      <c r="D32" t="str">
-        <v>overcome(克服)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>spontaneous</v>
       </c>
       <c r="B33" t="str">
-        <v>spontaneous</v>
+        <v>/spɑːnˈteɪniəs/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>自发的</v>
       </c>
-      <c r="D33" t="str">
-        <v>spontaneous(自发的)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>demand</v>
       </c>
       <c r="B34" t="str">
-        <v>demand</v>
+        <v>/dɪˈmænd/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D34" t="str">
         <v>要求</v>
       </c>
-      <c r="D34" t="str">
-        <v>demand(要求)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>pudding</v>
       </c>
       <c r="B35" t="str">
-        <v>pudding</v>
+        <v>/ˈpʊdɪŋ/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>布丁</v>
       </c>
-      <c r="D35" t="str">
-        <v>pudding(布丁)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>credit</v>
       </c>
       <c r="B36" t="str">
-        <v>credit</v>
+        <v>/ˈkredɪt/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D36" t="str">
         <v>信任</v>
       </c>
-      <c r="D36" t="str">
-        <v>credit(信任)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>intention</v>
       </c>
       <c r="B37" t="str">
-        <v>intention</v>
+        <v>/ɪnˈtenʃn/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>意图</v>
       </c>
-      <c r="D37" t="str">
-        <v>intention(意图)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>meanwhile</v>
       </c>
       <c r="B38" t="str">
-        <v>meanwhile</v>
+        <v>/ˈmiːnwaɪl/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D38" t="str">
         <v>同时</v>
       </c>
-      <c r="D38" t="str">
-        <v>meanwhile(同时)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>request</v>
       </c>
       <c r="B39" t="str">
-        <v>request</v>
+        <v>/rɪˈkwest/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D39" t="str">
         <v>请求</v>
       </c>
-      <c r="D39" t="str">
-        <v>request(请求)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>break</v>
       </c>
       <c r="B40" t="str">
-        <v>bad</v>
+        <v>/breɪk/</v>
       </c>
       <c r="C40" t="str">
-        <v>不孝的</v>
+        <v>n./v.</v>
       </c>
       <c r="D40" t="str">
-        <v>bad(不孝的)📢</v>
+        <v>打破</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>float</v>
       </c>
       <c r="B41" t="str">
-        <v>break</v>
+        <v>/floʊt/</v>
       </c>
       <c r="C41" t="str">
-        <v>打破</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>break(打破)📢</v>
+        <v>飘浮</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>memorial</v>
       </c>
       <c r="B42" t="str">
-        <v>float</v>
+        <v>/məˈmɔːriəl/</v>
       </c>
       <c r="C42" t="str">
-        <v>飘浮</v>
+        <v>n./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>float(飘浮)📢</v>
+        <v>纪念</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>proportional</v>
       </c>
       <c r="B43" t="str">
-        <v>memorial</v>
+        <v>/prəˈpɔːrʃənl/</v>
       </c>
       <c r="C43" t="str">
-        <v>纪念</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>memorial(纪念)📢</v>
+        <v>成比例的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>circuit</v>
       </c>
       <c r="B44" t="str">
-        <v>proportional</v>
+        <v>/ˈsɜːrkɪt/</v>
       </c>
       <c r="C44" t="str">
-        <v>成比例的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>proportional(成比例的)📢</v>
+        <v>电路</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>sting</v>
       </c>
       <c r="B45" t="str">
-        <v>circuit</v>
+        <v>/stɪŋ/</v>
       </c>
       <c r="C45" t="str">
-        <v>电路</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>circuit(电路)📢</v>
+        <v>刺痛</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>civilize</v>
       </c>
       <c r="B46" t="str">
-        <v>sting</v>
+        <v>/ˈsɪvəlaɪz/</v>
       </c>
       <c r="C46" t="str">
-        <v>刺痛</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>sting(刺痛)📢</v>
+        <v>教化</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>seed</v>
       </c>
       <c r="B47" t="str">
-        <v>amaze</v>
+        <v>/siːd/</v>
       </c>
       <c r="C47" t="str">
-        <v>不可思议</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>amaze(不可思议)📢</v>
+        <v>种子</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>length</v>
       </c>
       <c r="B48" t="str">
-        <v>bad</v>
+        <v>/leŋkθ/</v>
       </c>
       <c r="C48" t="str">
-        <v>坏</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>bad(坏)📢</v>
+        <v>长度</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>wash</v>
       </c>
       <c r="B49" t="str">
-        <v>civilize</v>
+        <v>/wɑːʃ/</v>
       </c>
       <c r="C49" t="str">
-        <v>教化</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>civilize(教化)📢</v>
+        <v>洗涤</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>hay</v>
       </c>
       <c r="B50" t="str">
-        <v>bad</v>
+        <v>/heɪ/</v>
       </c>
       <c r="C50" t="str">
-        <v>很差</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>bad(很差)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>seed</v>
-      </c>
-      <c r="C51" t="str">
-        <v>种子</v>
-      </c>
-      <c r="D51" t="str">
-        <v>seed(种子)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>length</v>
-      </c>
-      <c r="C52" t="str">
-        <v>长度</v>
-      </c>
-      <c r="D52" t="str">
-        <v>length(长度)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>wash</v>
-      </c>
-      <c r="C53" t="str">
-        <v>洗涤</v>
-      </c>
-      <c r="D53" t="str">
-        <v>wash(洗涤)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>hay</v>
-      </c>
-      <c r="C54" t="str">
         <v>干草</v>
-      </c>
-      <c r="D54" t="str">
-        <v>hay(干草)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>